--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>93.69957850717802</v>
+        <v>15.22618150741643</v>
       </c>
       <c r="D2" t="n">
-        <v>44.26240937682372</v>
+        <v>7.192641523733855</v>
       </c>
       <c r="E2" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F2" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>84.73605494240196</v>
+        <v>13.76960892814032</v>
       </c>
       <c r="D3" t="n">
-        <v>41.2361536392926</v>
+        <v>6.700874966385047</v>
       </c>
       <c r="E3" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F3" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.43657621515831</v>
+        <v>3.645943634963225</v>
       </c>
       <c r="D4" t="n">
-        <v>22.72846721059121</v>
+        <v>3.693375921721072</v>
       </c>
       <c r="E4" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F4" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.28175828372046</v>
+        <v>9.470785721104575</v>
       </c>
       <c r="D5" t="n">
-        <v>36.00389724074147</v>
+        <v>5.850633301620489</v>
       </c>
       <c r="E5" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F5" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.43912065261134</v>
+        <v>6.733857106049344</v>
       </c>
       <c r="D6" t="n">
-        <v>41.82452673862493</v>
+        <v>6.796485595026552</v>
       </c>
       <c r="E6" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F6" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.16683126790767</v>
+        <v>8.477110081034997</v>
       </c>
       <c r="D7" t="n">
-        <v>47.44089629437062</v>
+        <v>7.709145647835227</v>
       </c>
       <c r="E7" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F7" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.07033327453832</v>
+        <v>6.673929157112477</v>
       </c>
       <c r="D8" t="n">
-        <v>46.08155997751014</v>
+        <v>7.488253496345398</v>
       </c>
       <c r="E8" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F8" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.94987827553041</v>
+        <v>9.254355219773691</v>
       </c>
       <c r="D9" t="n">
-        <v>57.9156248997237</v>
+        <v>9.411289046205102</v>
       </c>
       <c r="E9" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F9" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.72718923103566</v>
+        <v>8.243168250043295</v>
       </c>
       <c r="D10" t="n">
-        <v>48.95941341637273</v>
+        <v>7.955904680160568</v>
       </c>
       <c r="E10" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F10" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.936635064760721</v>
+        <v>1.127203198023617</v>
       </c>
       <c r="D11" t="n">
-        <v>5.881479249228535</v>
+        <v>0.955740377999637</v>
       </c>
       <c r="E11" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F11" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.04937822564224</v>
+        <v>3.095523961666865</v>
       </c>
       <c r="D12" t="n">
-        <v>2.91547594742265</v>
+        <v>0.4737648414561807</v>
       </c>
       <c r="E12" t="n">
-        <v>25.07710524994096</v>
+        <v>4.075029603115406</v>
       </c>
       <c r="F12" t="n">
-        <v>17.02451779620523</v>
+        <v>2.76648414188335</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
